--- a/eda/ket_qua/ket_qua_modelSVM.xlsx
+++ b/eda/ket_qua/ket_qua_modelSVM.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,32 @@
         <v>134</v>
       </c>
       <c r="H2" t="n">
+        <v>0.624113475177305</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.7839506172839507</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7705627705627706</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7711390635918938</v>
+      </c>
+      <c r="D3" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.624113475177305</v>
       </c>
     </row>

--- a/eda/ket_qua/ket_qua_modelSVM.xlsx
+++ b/eda/ket_qua/ket_qua_modelSVM.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,32 +493,6 @@
         <v>134</v>
       </c>
       <c r="H2" t="n">
-        <v>0.624113475177305</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.7839506172839507</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.7705627705627706</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.7711390635918938</v>
-      </c>
-      <c r="D3" t="n">
-        <v>44</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F3" t="n">
-        <v>37</v>
-      </c>
-      <c r="G3" t="n">
-        <v>134</v>
-      </c>
-      <c r="H3" t="n">
         <v>0.624113475177305</v>
       </c>
     </row>
